--- a/Assets/_OriginalData/Excel/Config/MiniGame/MiniType.xlsx
+++ b/Assets/_OriginalData/Excel/Config/MiniGame/MiniType.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21630" windowHeight="9030"/>
+    <workbookView windowWidth="23715" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="Screw" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -185,6 +185,9 @@
     <t>Bus</t>
   </si>
   <si>
+    <t>BusOut</t>
+  </si>
+  <si>
     <t>Packed Bus</t>
   </si>
   <si>
@@ -201,6 +204,9 @@
   </si>
   <si>
     <t>Triple</t>
+  </si>
+  <si>
+    <t>TripleMath</t>
   </si>
   <si>
     <t>Triple Hunting</t>
@@ -395,13 +401,13 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1431,22 +1437,22 @@
         <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -1458,25 +1464,25 @@
         <v>105</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
